--- a/examples/position-tags/规则_决策表.xlsx
+++ b/examples/position-tags/规则_决策表.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
   </fonts>
   <fills count="7">
     <fill>
@@ -95,52 +96,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -511,10 +515,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="90" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -567,7 +571,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>关键岗位清单</t>
@@ -588,7 +592,7 @@
           <t>关键岗位清单.xlsx</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>清单文件就是一个参照表: 按 岗位编码 对齐到主表, 关键岗位清单.存在 = 这个岗位在不在清单里 (issue #15 的「属于文件」)</t>
         </is>
@@ -608,9 +612,9 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -636,7 +640,7 @@
           <t>基准日期</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="6" t="n">
         <v>46296</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -693,9 +697,9 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -715,7 +719,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>职级数</t>
@@ -726,13 +730,13 @@
           <t>数字(岗位.职级)</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>文本里的第一个数: 22级 / 23 / P23 -&gt; 22 / 23 / 23; 取不到 (空格或没有数字) 为空, 空值不参与 &gt;= 比较</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>近一年推荐</t>
@@ -743,7 +747,7 @@
           <t>岗位.推荐时间 &gt;= 基准日期 - 365天</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>N天 是时长字面量, 可以加减日期; 推荐时间为空不成立。等价写法: 天数差(基准日期, 岗位.推荐时间) &lt;= 365</t>
         </is>
@@ -767,27 +771,27 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>空值</t>
         </is>
       </c>
       <c r="B6" s="3" t="n"/>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>x == 空 / x != 空 判空 (也认 为空(x) / 非空(x)); 空 只能和 == / != 搭配, 不能参与大小比较和运算</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="47" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>可用函数</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, ...)  包含 / 不包含 / 开头是 / 开头不是 / 结尾是 / 结尾不是 (x, 文本1, ...)  拼接(a, b, ...)  数字(x)  如果(条件, 真值, 假值)</t>
         </is>
@@ -809,14 +813,14 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="64" customWidth="1" min="9" max="9"/>
-    <col width="90" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -825,7 +829,7 @@
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>多条拼接</t>
         </is>
@@ -837,394 +841,394 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>岗位.岗位名称</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>岗位.一层组织</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>关键岗位清单.存在</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>职级数</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>近一年推荐</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>标签</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>包含 CEO, 总裁</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>高管</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>子串匹配, 任一命中即真。按字面匹配不是正则; 注意「总裁助理」也含「总裁」, 要精确就用 开头是 / 等于</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>不包含 助理</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>开头是 2-, 3-</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>直管</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>同一行各格 AND: 一层组织以 2- 或 3- 开头, 且名称不含 助理。不包含 对空值也不成立 (空值参与任何比较都不成立)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>关键岗位</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>清单文件当参照表, 存在 = 在清单里</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>&gt;= 23</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>高职级</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>职级数 是变量定义里用 数字() 剥掉「级」后缀得到的; 单元格里只写比较</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>G5</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>新推荐</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>近一年推荐 是布尔派生变量, 单元格写 是</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="9" ht="47" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>G9</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1234,7 +1238,7 @@
           <t>=如果(岗位.一层组织 != 空, 拼接(岗位.一层组织, "/", 岗位.岗位名称), 岗位.岗位名称)</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>无条件; 多条拼接 下只有它写 显示名, 所以不发生拼接。如果() 是向量化三元, 条件为空走假分支</t>
         </is>
@@ -1254,144 +1258,144 @@
   <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>岗位.岗位名称</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>岗位.一层组织</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>关键岗位清单.存在</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>岗位.职级</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>岗位.推荐时间</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>岗位.标签</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>标签</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>集团CEO</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>1-集团总部</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>22级</t>
         </is>
@@ -1399,45 +1403,45 @@
       <c r="F3" s="15" t="n">
         <v>46174</v>
       </c>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="G3" s="12" t="n"/>
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>高管/新推荐</t>
         </is>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>1-集团总部/集团CEO</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>两条命中, 按优先级顺序拼接</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>华东代表处-行政助理</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>3-华东代表处</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>20级</t>
         </is>
@@ -1445,89 +1449,89 @@
       <c r="F4" s="15" t="n">
         <v>45658</v>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>3-华东代表处/华东代表处-行政助理</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>名称含 助理, G2 不命中; 标签期望留空 = 保持 普通</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>华东代表处-代表</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>3-华东代表处</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>23级</t>
         </is>
       </c>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>待定</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>直管/关键岗位/高职级</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>3-华东代表处/华东代表处-代表</t>
         </is>
       </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>原标签 待定 被整体替换; 职级数 / 近一年推荐 两列不在用例里, 按变量定义推导</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>法务经理</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>19级</t>
         </is>
@@ -1535,45 +1539,45 @@
       <c r="F6" s="15" t="n">
         <v>46054</v>
       </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>新推荐</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>法务经理</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>一层组织为空: 如果() 走假分支, 显示名只有岗位名称</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>研发-SPDT主管</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>4-研发体系</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>P23</t>
         </is>
@@ -1581,87 +1585,87 @@
       <c r="F7" s="15" t="n">
         <v>45657</v>
       </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>关键岗位/高职级</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>4-研发体系/研发-SPDT主管</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>P23 -&gt; 23; 推荐超过一年不算新推荐</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>财务部-会计</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>5-职能平台</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n"/>
+      <c r="E8" s="12" t="n"/>
       <c r="F8" s="15" t="n">
         <v>46296</v>
       </c>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>新推荐</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>5-职能平台/财务部-会计</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>职级为空, 数字() 取不到, &gt;= 23 不成立</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>供应链-采购经理</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>6-供应链</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>22级</t>
         </is>
@@ -1669,45 +1673,45 @@
       <c r="F9" s="15" t="n">
         <v>45931</v>
       </c>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>新推荐</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t>6-供应链/供应链-采购经理</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>正好 365 天, &gt;= 成立</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>T8</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>供应链-采购经理</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>6-供应链</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>22级</t>
         </is>
@@ -1715,14 +1719,14 @@
       <c r="F10" s="15" t="n">
         <v>45930</v>
       </c>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="13" t="n"/>
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>6-供应链/供应链-采购经理</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>366 天, 不算; 标签期望留空 = 不变 (原本就空)</t>
         </is>

--- a/examples/position-tags/规则_决策表.xlsx
+++ b/examples/position-tags/规则_决策表.xlsx
@@ -609,12 +609,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>基准日期</t>
@@ -643,43 +643,61 @@
       <c r="B2" s="6" t="n">
         <v>46296</v>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>「近一年推荐」以它为准; 不填取运行当天</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>天数差 / N天 等日期计算用的「今天」(本表的「近一年推荐」以它为准), 日期格或 2026-10-01 文本都行。留空取运行当天</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>output/岗位清单_更新后.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>拼接分隔符</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>命中策略 多条拼接 用的分隔符, 默认就是 /</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>output/岗位清单_更新后.xlsx</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>默认输出路径, 命令行 -o 可覆盖</t>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>命中策略 多条拼接 用的分隔符, 留空为 /; 策略不是 多条拼接 时填了会报错</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>可用设置项</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>只认上面三个, 写别的加载时报错 (不会静默忽略); 只读 A 列 (设置项) 和 B 列 (值), B 列留空 = 取默认值; 本列是说明, 不参与解析</t>
         </is>
       </c>
     </row>

--- a/examples/position-tags/规则_决策表.xlsx
+++ b/examples/position-tags/规则_决策表.xlsx
@@ -826,19 +826,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -904,7 +905,12 @@
           <t>输出</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -953,10 +959,15 @@
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
+          <t>职能</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -1006,7 +1017,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>子串匹配, 任一命中即真。按字面匹配不是正则; 注意「总裁助理」也含「总裁」, 要精确就用 开头是 / 等于</t>
         </is>
@@ -1056,7 +1072,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>同一行各格 AND: 一层组织以 2- 或 3- 开头, 且名称不含 助理。不包含 对空值也不成立 (空值参与任何比较都不成立)</t>
         </is>
@@ -1106,7 +1127,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>清单文件当参照表, 存在 = 在清单里</t>
         </is>
@@ -1156,7 +1182,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>职级数 是变量定义里用 数字() 剥掉「级」后缀得到的; 单元格里只写比较</t>
         </is>
@@ -1206,63 +1237,279 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>近一年推荐 是布尔派生变量, 单元格写 是</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="47" customHeight="1">
+    <row r="9" ht="62" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>开头是 5-</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>职能平台</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>相邻同 ID 的四行各自填了不同的输出 = 有各自输出的分支 (0.7): 规则整体计一次, 审计记 G6; 多条拼接 下成立的几支接起来 (5-职能平台 的 财务部-会计 是 职能平台/财务), 其它策略下取书写顺序第一个成立的</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>包含 财务, 会计</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>财务</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>G6 的第二支。续行的输出格留空 = 与首行相同 (单纯的「或」), 写了不同的值 = 自己的输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>包含 法务</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>法务</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>G6 的第三支</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>包含 采购, 供应</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>供应链</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>G6 的第四支</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="47" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
           <t>G9</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B13" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>=如果(岗位.一层组织 != 空, 拼接(岗位.一层组织, "/", 岗位.岗位名称), 岗位.岗位名称)</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>无条件; 多条拼接 下只有它写 显示名, 所以不发生拼接。如果() 是向量化三元, 条件为空走假分支</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A9:A12"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1273,7 +1520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1284,8 +1531,9 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1334,7 +1582,12 @@
           <t>期望</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>期望</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -1383,10 +1636,15 @@
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
+          <t>职能</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="K2" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -1427,12 +1685,13 @@
           <t>高管/新推荐</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="13" t="n"/>
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>1-集团总部/集团CEO</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>两条命中, 按优先级顺序拼接</t>
         </is>
@@ -1473,12 +1732,13 @@
         </is>
       </c>
       <c r="H4" s="13" t="n"/>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="13" t="n"/>
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>3-华东代表处/华东代表处-行政助理</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>名称含 助理, G2 不命中; 标签期望留空 = 保持 普通</t>
         </is>
@@ -1521,18 +1781,19 @@
           <t>直管/关键岗位/高职级</t>
         </is>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>3-华东代表处/华东代表处-代表</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>原标签 待定 被整体替换; 职级数 / 近一年推荐 两列不在用例里, 按变量定义推导</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>T4</t>
@@ -1565,12 +1826,17 @@
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
+          <t>法务</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
           <t>法务经理</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>一层组织为空: 如果() 走假分支, 显示名只有岗位名称</t>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>一层组织为空: 如果() 走假分支, 显示名只有岗位名称; G6 只有 法务 一支成立</t>
         </is>
       </c>
     </row>
@@ -1609,18 +1875,19 @@
           <t>关键岗位/高职级</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>4-研发体系/研发-SPDT主管</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>P23 -&gt; 23; 推荐超过一年不算新推荐</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>T6</t>
@@ -1653,12 +1920,17 @@
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
+          <t>职能平台/财务</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
           <t>5-职能平台/财务部-会计</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>职级为空, 数字() 取不到, &gt;= 23 不成立</t>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>职级为空, 数字() 取不到, &gt;= 23 不成立; G6 两支都成立 (5-职能平台 + 会计), 多条拼接 下接起来</t>
         </is>
       </c>
     </row>
@@ -1699,10 +1971,15 @@
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
+          <t>供应链</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
           <t>6-供应链/供应链-采购经理</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>正好 365 天, &gt;= 成立</t>
         </is>
@@ -1741,10 +2018,15 @@
       <c r="H10" s="13" t="n"/>
       <c r="I10" s="13" t="inlineStr">
         <is>
+          <t>供应链</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
           <t>6-供应链/供应链-采购经理</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>366 天, 不算; 标签期望留空 = 不变 (原本就空)</t>
         </is>

--- a/examples/position-tags/规则_决策表.xlsx
+++ b/examples/position-tags/规则_决策表.xlsx
@@ -7,11 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="输入" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="设置" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="变量定义" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="决策表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="测试" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="设置" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="变量定义" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="决策表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="测试" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,12 +45,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -98,23 +97,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -125,7 +124,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -511,11 +510,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
@@ -524,75 +523,120 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>基准日期</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>天数差 / N天 等日期计算用的「今天」(本表的「近一年推荐」以它为准), 日期格或 2026-10-01 文本都行。留空取运行当天</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>output/岗位清单_更新后.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>可用设置项</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>只认 基准日期 / 输出, 写别的加载时报错 (不会静默忽略); B 列留空 = 取默认值。拼接分隔符 写在决策表左上角。下面「名称 / 匹配」那一行起是输入表</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>岗位</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>岗位清单.xlsx</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 岗位.岗位名称</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>关键岗位清单</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>取第一条</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>关键岗位清单.xlsx</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>清单文件就是一个参照表: 按 岗位编码 对齐到主表, 关键岗位清单.存在 = 这个岗位在不在清单里 (issue #15 的「属于文件」)</t>
         </is>
@@ -604,109 +648,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>设置项</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>值</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>基准日期</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>天数差 / N天 等日期计算用的「今天」(本表的「近一年推荐」以它为准), 日期格或 2026-10-01 文本都行。留空取运行当天</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>output/岗位清单_更新后.xlsx</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>拼接分隔符</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>命中策略 多条拼接 用的分隔符, 留空为 /; 策略不是 多条拼接 时填了会报错</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>可用设置项</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>只认上面三个, 写别的加载时报错 (不会静默忽略); 只读 A 列 (设置项) 和 B 列 (值), B 列留空 = 取默认值; 本列是说明, 不参与解析</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -721,95 +662,95 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>变量</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>定义</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>职级数</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>数字(岗位.职级)</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>文本里的第一个数: 22级 / 23 / P23 -&gt; 22 / 23 / 23; 取不到 (空格或没有数字) 为空, 空值不参与 &gt;= 比较</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>近一年推荐</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>岗位.推荐时间 &gt;= 基准日期 - 365天</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>N天 是时长字面量, 可以加减日期; 推荐时间为空不成立。等价写法: 天数差(基准日期, 岗位.推荐时间) &lt;= 365</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="4" t="n"/>
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>连接词</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>且 / 或 / 非 (也认 and / or / not), 两侧留空格; 可用括号分组</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>空值</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>x == 空 / x != 空 判空 (也认 为空(x) / 非空(x)); 空 只能和 == / != 搭配, 不能参与大小比较和运算</t>
         </is>
       </c>
     </row>
     <row r="7" ht="47" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>可用函数</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, ...)  包含 / 不包含 / 开头是 / 开头不是 / 结尾是 / 结尾不是 (x, 文本1, ...)  拼接(a, b, ...)  数字(x)  如果(条件, 真值, 假值)</t>
         </is>
@@ -820,13 +761,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -843,76 +784,36 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>多条拼接</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>每个输出列把所有命中规则写的值按优先级顺序用「拼接分隔符」接起来 (DMN 的 Collect); 没命中的行不动, 原值被整体替换</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>规则ID</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>输入</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>输入</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>输入</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>输入</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>输入</t>
-        </is>
-      </c>
-      <c r="H2" s="9" t="inlineStr">
-        <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="J2" s="9" t="inlineStr">
-        <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="K2" s="10" t="inlineStr">
-        <is>
-          <t>说明</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>拼接分隔符</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>多条拼接 用的分隔符, 留空为 /; 和命中策略写在一起 (策略不是 多条拼接 时写了会报错)</t>
         </is>
       </c>
     </row>
@@ -929,435 +830,443 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>规则ID</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
           <t>岗位.岗位名称</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>岗位.一层组织</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>关键岗位清单.存在</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>职级数</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>近一年推荐</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>标签</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>职能</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>包含 CEO, 总裁</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>高管</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>子串匹配, 任一命中即真。按字面匹配不是正则; 注意「总裁助理」也含「总裁」, 要精确就用 开头是 / 等于</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>包含 CEO, 总裁</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>高管</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>子串匹配, 任一命中即真。按字面匹配不是正则; 注意「总裁助理」也含「总裁」, 要精确就用 开头是 / 等于</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>不包含 助理</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>开头是 2-, 3-</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>直管</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>同一行各格 AND: 一层组织以 2- 或 3- 开头, 且名称不含 助理。不包含 对空值也不成立 (空值参与任何比较都不成立)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B7" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>关键岗位</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>清单文件当参照表, 存在 = 在清单里</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>&gt;= 23</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>高职级</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>职级数 是变量定义里用 数字() 剥掉「级」后缀得到的; 单元格里只写比较</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>G5</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B9" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>新推荐</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>近一年推荐 是布尔派生变量, 单元格写 是</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>G6</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B10" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>开头是 5-</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>职能平台</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>相邻同 ID 的四行各自填了不同的输出 = 有各自输出的分支 (0.7): 规则整体计一次, 审计记 G6; 多条拼接 下成立的几支接起来 (5-职能平台 的 财务部-会计 是 职能平台/财务), 其它策略下取书写顺序第一个成立的</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>包含 财务, 会计</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>财务</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>G6 的第二支。续行的输出格留空 = 与首行相同 (单纯的「或」), 写了不同的值 = 自己的输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+    <row r="11" ht="32" customHeight="1">
       <c r="A11" s="11" t="n"/>
       <c r="B11" s="11" t="n"/>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>包含 法务</t>
+          <t>包含 财务, 会计</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1387,7 +1296,7 @@
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>法务</t>
+          <t>财务</t>
         </is>
       </c>
       <c r="J11" s="13" t="inlineStr">
@@ -1395,9 +1304,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>G6 的第三支</t>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>G6 的第二支。续行的输出格留空 = 与首行相同 (单纯的「或」), 写了不同的值 = 自己的输出</t>
         </is>
       </c>
     </row>
@@ -1406,100 +1315,149 @@
       <c r="B12" s="11" t="n"/>
       <c r="C12" s="12" t="inlineStr">
         <is>
+          <t>包含 法务</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>法务</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>G6 的第三支</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
           <t>包含 采购, 供应</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>供应链</t>
         </is>
       </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>G6 的第四支</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="47" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+    <row r="14" ht="47" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>G9</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B14" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>=如果(岗位.一层组织 != 空, 拼接(岗位.一层组织, "/", 岗位.岗位名称), 岗位.岗位名称)</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>无条件; 多条拼接 下只有它写 显示名, 所以不发生拼接。如果() 是向量化三元, 条件为空走假分支</t>
         </is>
@@ -1507,14 +1465,14 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="A10:A13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1691,7 +1649,7 @@
           <t>1-集团总部/集团CEO</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>两条命中, 按优先级顺序拼接</t>
         </is>
@@ -1738,7 +1696,7 @@
           <t>3-华东代表处/华东代表处-行政助理</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>名称含 助理, G2 不命中; 标签期望留空 = 保持 普通</t>
         </is>
@@ -1787,7 +1745,7 @@
           <t>3-华东代表处/华东代表处-代表</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>原标签 待定 被整体替换; 职级数 / 近一年推荐 两列不在用例里, 按变量定义推导</t>
         </is>
@@ -1834,7 +1792,7 @@
           <t>法务经理</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>一层组织为空: 如果() 走假分支, 显示名只有岗位名称; G6 只有 法务 一支成立</t>
         </is>
@@ -1881,7 +1839,7 @@
           <t>4-研发体系/研发-SPDT主管</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>P23 -&gt; 23; 推荐超过一年不算新推荐</t>
         </is>
@@ -1928,7 +1886,7 @@
           <t>5-职能平台/财务部-会计</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>职级为空, 数字() 取不到, &gt;= 23 不成立; G6 两支都成立 (5-职能平台 + 会计), 多条拼接 下接起来</t>
         </is>
@@ -1979,7 +1937,7 @@
           <t>6-供应链/供应链-采购经理</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>正好 365 天, &gt;= 成立</t>
         </is>
@@ -2026,7 +1984,7 @@
           <t>6-供应链/供应链-采购经理</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>366 天, 不算; 标签期望留空 = 不变 (原本就空)</t>
         </is>

--- a/examples/position-tags/规则_决策表.xlsx
+++ b/examples/position-tags/规则_决策表.xlsx
@@ -100,10 +100,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -510,133 +510,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="15.2" customWidth="1" min="1" max="1"/>
+    <col width="30.4" customWidth="1" min="2" max="2"/>
+    <col width="10.8" customWidth="1" min="3" max="3"/>
+    <col width="20.2" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>基准日期</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>天数差 / N天 等日期计算用的「今天」(本表的「近一年推荐」以它为准), 日期格或 2026-10-01 文本都行。留空取运行当天</t>
+          <t>设置项</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>每行一项: A 列名字 / B 列值 / 再往右是说明; 只认 基准日期 / 输出, 写别的加载时报错; B 列留空 = 取默认值</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>output/岗位清单_更新后.xlsx</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
+          <t>基准日期</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>天数差 / N天 等日期计算用的「今天」(本表的「近一年推荐」以它为准), 日期格或 2026-10-01 文本都行。留空取运行当天</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>可用设置项</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>只认 基准日期 / 输出, 写别的加载时报错 (不会静默忽略); B 列留空 = 取默认值。拼接分隔符 写在决策表左上角。下面「名称 / 匹配」那一行起是输入表</t>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>output/岗位清单_更新后.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>输入表</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>下一行是列名, 之后每行声明一个输入: 名称 = 规则里的前缀; 匹配 = 主表写 主表, 其它写对齐到主表的键; 文件 = 默认文件 (命令行 -i 可覆盖)。输入表下面不要再写别的</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>岗位</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>主表</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>岗位清单.xlsx</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 岗位.岗位名称</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>岗位</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>主表</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>岗位清单.xlsx</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 岗位.岗位名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
           <t>关键岗位清单</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>取第一条</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>关键岗位清单.xlsx</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>清单文件就是一个参照表: 按 岗位编码 对齐到主表, 关键岗位清单.存在 = 这个岗位在不在清单里 (issue #15 的「属于文件」)</t>
         </is>
@@ -656,8 +668,8 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="37.2" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -715,7 +727,7 @@
     <row r="4">
       <c r="A4" s="1" t="n"/>
       <c r="B4" s="4" t="n"/>
-      <c r="C4" s="3" t="n"/>
+      <c r="C4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -724,7 +736,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>且 / 或 / 非 (也认 and / or / not), 两侧留空格; 可用括号分组</t>
         </is>
@@ -770,15 +782,15 @@
   <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18.2" customWidth="1" min="3" max="3"/>
+    <col width="16.2" customWidth="1" min="4" max="4"/>
+    <col width="20.6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="10.8" customWidth="1" min="8" max="8"/>
+    <col width="10.8" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
@@ -789,12 +801,12 @@
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>多条拼接</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>每个输出列把所有命中规则写的值按优先级顺序用「拼接分隔符」接起来 (DMN 的 Collect); 没命中的行不动, 原值被整体替换</t>
         </is>
@@ -806,12 +818,12 @@
           <t>拼接分隔符</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>多条拼接 用的分隔符, 留空为 /; 和命中策略写在一起 (策略不是 多条拼接 时写了会报错)</t>
         </is>
@@ -1090,7 +1102,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>清单文件当参照表, 存在 = 在清单里</t>
         </is>
@@ -1200,7 +1212,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>近一年推荐 是布尔派生变量, 单元格写 是</t>
         </is>
@@ -1353,7 +1365,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>G6 的第三支</t>
         </is>
@@ -1402,7 +1414,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>G6 的第四支</t>
         </is>
@@ -1482,14 +1494,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="22.8" customWidth="1" min="2" max="2"/>
+    <col width="16.2" customWidth="1" min="3" max="3"/>
+    <col width="20.6" customWidth="1" min="4" max="4"/>
+    <col width="11.8" customWidth="1" min="5" max="5"/>
+    <col width="16.2" customWidth="1" min="6" max="6"/>
+    <col width="11.8" customWidth="1" min="7" max="7"/>
+    <col width="23.8" customWidth="1" min="8" max="8"/>
+    <col width="16.2" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
@@ -1649,7 +1661,7 @@
           <t>1-集团总部/集团CEO</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>两条命中, 按优先级顺序拼接</t>
         </is>
@@ -1696,7 +1708,7 @@
           <t>3-华东代表处/华东代表处-行政助理</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>名称含 助理, G2 不命中; 标签期望留空 = 保持 普通</t>
         </is>
@@ -1839,7 +1851,7 @@
           <t>4-研发体系/研发-SPDT主管</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>P23 -&gt; 23; 推荐超过一年不算新推荐</t>
         </is>
@@ -1937,7 +1949,7 @@
           <t>6-供应链/供应链-采购经理</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>正好 365 天, &gt;= 成立</t>
         </is>
@@ -1984,7 +1996,7 @@
           <t>6-供应链/供应链-采购经理</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>366 天, 不算; 标签期望留空 = 不变 (原本就空)</t>
         </is>

--- a/examples/position-tags/规则_决策表.xlsx
+++ b/examples/position-tags/规则_决策表.xlsx
@@ -510,14 +510,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.2" customWidth="1" min="1" max="1"/>
     <col width="30.4" customWidth="1" min="2" max="2"/>
-    <col width="10.8" customWidth="1" min="3" max="3"/>
-    <col width="20.2" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="39.8" customWidth="1" min="3" max="3"/>
+    <col width="10.8" customWidth="1" min="4" max="4"/>
+    <col width="20.2" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -590,15 +591,20 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
+          <t>筛选</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -616,18 +622,19 @@
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>岗位清单.xlsx</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 岗位.岗位名称</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
+    <row r="8" ht="62" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
           <t>关键岗位清单</t>
@@ -640,17 +647,22 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>关键岗位清单.配置类别 == "关键岗位"</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
           <t>取第一条</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>关键岗位清单.xlsx</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>清单文件就是一个参照表: 按 岗位编码 对齐到主表, 关键岗位清单.存在 = 这个岗位在不在清单里 (issue #15 的「属于文件」)</t>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>清单文件就是一个参照表: 按 岗位编码 对齐到主表, 关键岗位清单.存在 = 这个岗位在不在清单里 (issue #15 的「属于文件」)。这张清单混着两类配置, 筛选在对齐之前只留 关键岗位 这一类 (issue #30); 筛选是表达式, 只能引用这张表自己的列和 基准日期</t>
         </is>
       </c>
     </row>

--- a/examples/position-tags/规则_决策表.xlsx
+++ b/examples/position-tags/规则_决策表.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,15 +33,27 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font/>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -69,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -91,58 +103,113 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -521,152 +588,172 @@
     <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>设置项</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>每行一项: A 列名字 / B 列值 / 再往右是说明; 只认 基准日期 / 输出, 写别的加载时报错; B 列留空 = 取默认值</t>
         </is>
       </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>基准日期</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="7" t="n">
         <v>46296</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>天数差 / N天 等日期计算用的「今天」(本表的「近一年推荐」以它为准), 日期格或 2026-10-01 文本都行。留空取运行当天</t>
         </is>
       </c>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>output/岗位清单_更新后.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
         </is>
       </c>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4"/>
-    <row r="5">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>输入表</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>下一行是列名, 之后每行声明一个输入: 名称 = 规则里的前缀; 匹配 = 主表写 主表, 其它写对齐到主表的键; 文件 = 默认文件 (命令行 -i 可覆盖)。输入表下面不要再写别的</t>
         </is>
       </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>筛选</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>岗位</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>岗位清单.xlsx</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 岗位.岗位名称</t>
         </is>
       </c>
     </row>
     <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>关键岗位清单</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>关键岗位清单.配置类别 == "关键岗位"</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>取第一条</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>关键岗位清单.xlsx</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>清单文件就是一个参照表: 按 岗位编码 对齐到主表, 关键岗位清单.存在 = 这个岗位在不在清单里 (issue #15 的「属于文件」)。这张清单混着两类配置, 筛选在对齐之前只留 关键岗位 这一类 (issue #30); 筛选是表达式, 只能引用这张表自己的列和 基准日期</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C3:F3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -686,95 +773,95 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>变量</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>定义</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>职级数</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>数字(岗位.职级)</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>文本里的第一个数: 22级 / 23 / P23 -&gt; 22 / 23 / 23; 取不到 (空格或没有数字) 为空, 空值不参与 &gt;= 比较</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>近一年推荐</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>岗位.推荐时间 &gt;= 基准日期 - 365天</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>N天 是时长字面量, 可以加减日期; 推荐时间为空不成立。等价写法: 天数差(基准日期, 岗位.推荐时间) &lt;= 365</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n"/>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="2" t="n"/>
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="11" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>连接词</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>且 / 或 / 非 (也认 and / or / not), 两侧留空格; 可用括号分组</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>空值</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>x == 空 / x != 空 判空 (也认 为空(x) / 非空(x)); 空 只能和 == / != 搭配, 不能参与大小比较和运算</t>
         </is>
       </c>
     </row>
     <row r="7" ht="47" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>可用函数</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, ...)  包含 / 不包含 / 开头是 / 开头不是 / 结尾是 / 结尾不是 (x, 文本1, ...)  拼接(a, b, ...)  数字(x)  如果(条件, 真值, 假值)</t>
         </is>
@@ -808,687 +895,705 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>多条拼接</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>每个输出列把所有命中规则写的值按优先级顺序用「拼接分隔符」接起来 (DMN 的 Collect); 没命中的行不动, 原值被整体替换</t>
         </is>
       </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>拼接分隔符</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>多条拼接 用的分隔符, 留空为 /; 和命中策略写在一起 (策略不是 多条拼接 时写了会报错)</t>
         </is>
       </c>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>岗位.岗位名称</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>岗位.一层组织</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>关键岗位清单.存在</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>职级数</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>近一年推荐</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>标签</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>职能</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="K4" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>包含 CEO, 总裁</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>高管</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>子串匹配, 任一命中即真。按字面匹配不是正则; 注意「总裁助理」也含「总裁」, 要精确就用 开头是 / 等于</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>不包含 助理</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>开头是 2-, 3-</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>直管</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>同一行各格 AND: 一层组织以 2- 或 3- 开头, 且名称不含 助理。不包含 对空值也不成立 (空值参与任何比较都不成立)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>关键岗位</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>清单文件当参照表, 存在 = 在清单里</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>&gt;= 23</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>高职级</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>职级数 是变量定义里用 数字() 剥掉「级」后缀得到的; 单元格里只写比较</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>G5</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>新推荐</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
         <is>
           <t>近一年推荐 是布尔派生变量, 单元格写 是</t>
         </is>
       </c>
     </row>
     <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>G6</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>开头是 5-</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>职能平台</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>相邻同 ID 的四行各自填了不同的输出 = 有各自输出的分支 (0.7): 规则整体计一次, 审计记 G6; 多条拼接 下成立的几支接起来 (5-职能平台 的 财务部-会计 是 职能平台/财务), 其它策略下取书写顺序第一个成立的</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>包含 财务, 会计</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>财务</t>
         </is>
       </c>
-      <c r="J11" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>G6 的第二支。续行的输出格留空 = 与首行相同 (单纯的「或」), 写了不同的值 = 自己的输出</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>包含 法务</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>法务</t>
         </is>
       </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>G6 的第三支</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>包含 采购, 供应</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>供应链</t>
         </is>
       </c>
-      <c r="J13" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>G6 的第四支</t>
         </is>
       </c>
     </row>
     <row r="14" ht="47" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>G9</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="19" t="inlineStr">
         <is>
           <t>=如果(岗位.一层组织 != 空, 拼接(岗位.一层组织, "/", 岗位.岗位名称), 岗位.岗位名称)</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>无条件; 多条拼接 下只有它写 显示名, 所以不发生拼接。如果() 是向量化三元, 条件为空走假分支</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="C2:K2"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="A10:A13"/>
   </mergeCells>
@@ -1519,496 +1624,496 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>岗位.岗位名称</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>岗位.一层组织</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>关键岗位清单.存在</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>岗位.职级</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>岗位.推荐时间</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>岗位.标签</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>标签</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>职能</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="K2" s="10" t="inlineStr">
+      <c r="K2" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>集团CEO</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>1-集团总部</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>22级</t>
         </is>
       </c>
-      <c r="F3" s="15" t="n">
+      <c r="F3" s="20" t="n">
         <v>46174</v>
       </c>
-      <c r="G3" s="12" t="n"/>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="G3" s="17" t="n"/>
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>高管/新推荐</t>
         </is>
       </c>
-      <c r="I3" s="13" t="n"/>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="I3" s="18" t="n"/>
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>1-集团总部/集团CEO</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t>两条命中, 按优先级顺序拼接</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>华东代表处-行政助理</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>3-华东代表处</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>20级</t>
         </is>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="20" t="n">
         <v>45658</v>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
-      <c r="I4" s="13" t="n"/>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="H4" s="18" t="n"/>
+      <c r="I4" s="18" t="n"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t>3-华东代表处/华东代表处-行政助理</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>名称含 助理, G2 不命中; 标签期望留空 = 保持 普通</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>华东代表处-代表</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>3-华东代表处</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>23级</t>
         </is>
       </c>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>待定</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>直管/关键岗位/高职级</t>
         </is>
       </c>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="I5" s="18" t="n"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>3-华东代表处/华东代表处-代表</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>原标签 待定 被整体替换; 职级数 / 近一年推荐 两列不在用例里, 按变量定义推导</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>法务经理</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>19级</t>
         </is>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="20" t="n">
         <v>46054</v>
       </c>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="G6" s="17" t="n"/>
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>新推荐</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>法务</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>法务经理</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>一层组织为空: 如果() 走假分支, 显示名只有岗位名称; G6 只有 法务 一支成立</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>研发-SPDT主管</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>4-研发体系</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>P23</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="20" t="n">
         <v>45657</v>
       </c>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>关键岗位/高职级</t>
         </is>
       </c>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>4-研发体系/研发-SPDT主管</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>P23 -&gt; 23; 推荐超过一年不算新推荐</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>财务部-会计</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>5-职能平台</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="15" t="n">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="20" t="n">
         <v>46296</v>
       </c>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="G8" s="17" t="n"/>
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>新推荐</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>职能平台/财务</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>5-职能平台/财务部-会计</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>职级为空, 数字() 取不到, &gt;= 23 不成立; G6 两支都成立 (5-职能平台 + 会计), 多条拼接 下接起来</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>供应链-采购经理</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>6-供应链</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>22级</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="20" t="n">
         <v>45931</v>
       </c>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>新推荐</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>供应链</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>6-供应链/供应链-采购经理</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="11" t="inlineStr">
         <is>
           <t>正好 365 天, &gt;= 成立</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>T8</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>供应链-采购经理</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>6-供应链</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>22级</t>
         </is>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="F10" s="20" t="n">
         <v>45930</v>
       </c>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>供应链</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>6-供应链/供应链-采购经理</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>366 天, 不算; 标签期望留空 = 不变 (原本就空)</t>
         </is>
